--- a/src/main/resources/templates/xlsx/user-register-template.xlsx
+++ b/src/main/resources/templates/xlsx/user-register-template.xlsx
@@ -474,6 +474,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="잘못된 입력" error="훈련생, 강사, 매니저 중 하나를 선택해주세요." promptTitle="역할 선택" prompt="역할을 선택하세요" type="list">
+      <formula1>"훈련생,강사,매니저"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>